--- a/审核导出/silicone_glow_ink_审核.xlsx
+++ b/审核导出/silicone_glow_ink_审核.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>中國厂 / 手落機：50.8 X 127 / 自動機：305 X 483 / 越南厂 / a.ASP-1300 / 最小印張：840*350 / b.ST-1050 / 最小印張：560*350</t>
+          <t>中國廠 / 手落機：50.8 X 127 / 自動機：305 X 483 / 越南廠 / a.ASP-1300 / 最小印張：840*350 / b.ST-1050 / 最小印張：560*350</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="Y1" s="3" t="inlineStr">
